--- a/formulaciones.xlsx
+++ b/formulaciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\heber\Desktop\proyecto 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{786F8C4B-8258-4217-99AD-3317FF45E7B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93251B8E-277B-47E5-9B05-2D39F3285376}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{692A3B6C-7927-4F0A-B9F6-05DDFF7A8E26}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="114">
   <si>
     <t>Tratamiento</t>
   </si>
@@ -3776,1033 +3776,13 @@
   </si>
   <si>
     <t>Cotensoactivo</t>
-  </si>
-  <si>
-    <r>
-      <t>21.8892</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Symbol"/>
-        <family val="1"/>
-        <charset val="2"/>
-      </rPr>
-      <t>±</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>2.01</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>cd</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>0.1158</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Symbol"/>
-        <family val="1"/>
-        <charset val="2"/>
-      </rPr>
-      <t>±</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>0.05</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>efgh</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>17.3608</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Symbol"/>
-        <family val="1"/>
-        <charset val="2"/>
-      </rPr>
-      <t>±</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>0.24</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>d</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>0.0572</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Symbol"/>
-        <family val="1"/>
-        <charset val="2"/>
-      </rPr>
-      <t>±</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>0.00</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>h</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>37.2392</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Symbol"/>
-        <family val="1"/>
-        <charset val="2"/>
-      </rPr>
-      <t>±</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>31.77</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>cd</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>0.1740</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Symbol"/>
-        <family val="1"/>
-        <charset val="2"/>
-      </rPr>
-      <t>±</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>0.11</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>cdef</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>168.7167</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Symbol"/>
-        <family val="1"/>
-        <charset val="2"/>
-      </rPr>
-      <t>±</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>10.49</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>a</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>0.2468</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Symbol"/>
-        <family val="1"/>
-        <charset val="2"/>
-      </rPr>
-      <t>±</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>0.01</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>bcd</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>95.3283</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Symbol"/>
-        <family val="1"/>
-        <charset val="2"/>
-      </rPr>
-      <t>±</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>29.12</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>b</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>0.2763</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Symbol"/>
-        <family val="1"/>
-        <charset val="2"/>
-      </rPr>
-      <t>±</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>0.00</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>ab</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>114.3342</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Symbol"/>
-        <family val="1"/>
-        <charset val="2"/>
-      </rPr>
-      <t>±</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>55.68</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>b</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>0.2640</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Symbol"/>
-        <family val="1"/>
-        <charset val="2"/>
-      </rPr>
-      <t>±</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>0.02</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>abc</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>53.3742</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Symbol"/>
-        <family val="1"/>
-        <charset val="2"/>
-      </rPr>
-      <t>±</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>8.92</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>c</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>0.2358</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Symbol"/>
-        <family val="1"/>
-        <charset val="2"/>
-      </rPr>
-      <t>±</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>0.01</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>bcd</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>22.0425</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Symbol"/>
-        <family val="1"/>
-        <charset val="2"/>
-      </rPr>
-      <t>±</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>4.14</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>cd</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>0.3507</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Symbol"/>
-        <family val="1"/>
-        <charset val="2"/>
-      </rPr>
-      <t>±</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>0.07</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>a</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>13.1133</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Symbol"/>
-        <family val="1"/>
-        <charset val="2"/>
-      </rPr>
-      <t>±</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>0.60</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>d</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>0.1169</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Symbol"/>
-        <family val="1"/>
-        <charset val="2"/>
-      </rPr>
-      <t>±</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>0.05</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>efgh</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>98.2367</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Symbol"/>
-        <family val="1"/>
-        <charset val="2"/>
-      </rPr>
-      <t>±</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>52.50</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>b</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>0.2563</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Symbol"/>
-        <family val="1"/>
-        <charset val="2"/>
-      </rPr>
-      <t>±</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>0.04</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>abcd</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>28.2000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Symbol"/>
-        <family val="1"/>
-        <charset val="2"/>
-      </rPr>
-      <t>±</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>4.96</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>cd</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>0.1834</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Symbol"/>
-        <family val="1"/>
-        <charset val="2"/>
-      </rPr>
-      <t>±</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>0.015</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>bcde</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>15.1783</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Symbol"/>
-        <family val="1"/>
-        <charset val="2"/>
-      </rPr>
-      <t>±</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>2.48</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>d</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>0.0762</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Symbol"/>
-        <family val="1"/>
-        <charset val="2"/>
-      </rPr>
-      <t>±</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>0.02</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>fgh</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>13.6575</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Symbol"/>
-        <family val="1"/>
-        <charset val="2"/>
-      </rPr>
-      <t>±</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>1.22</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>d</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>0.1236</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Symbol"/>
-        <family val="1"/>
-        <charset val="2"/>
-      </rPr>
-      <t>±</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>0.07</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>efgh</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>22.8875</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Symbol"/>
-        <family val="1"/>
-        <charset val="2"/>
-      </rPr>
-      <t>±</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>5.28</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>cd</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>0.1601</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Symbol"/>
-        <family val="1"/>
-        <charset val="2"/>
-      </rPr>
-      <t>±</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>0.13</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>defg</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>16.1733</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Symbol"/>
-        <family val="1"/>
-        <charset val="2"/>
-      </rPr>
-      <t>±</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>0.97</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>d</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>0.0659</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Symbol"/>
-        <family val="1"/>
-        <charset val="2"/>
-      </rPr>
-      <t>±</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>0.00</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>gh</t>
-    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4856,13 +3836,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <vertAlign val="superscript"/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -6326,305 +5299,125 @@
         <v>111</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="20">
-        <v>43</v>
-      </c>
-      <c r="B45" s="14">
-        <v>250</v>
-      </c>
-      <c r="C45" s="15">
-        <v>600</v>
-      </c>
-      <c r="D45" s="15">
-        <v>200</v>
-      </c>
-      <c r="E45" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="F45" s="16" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="20">
-        <v>44</v>
-      </c>
-      <c r="B46" s="17">
-        <v>250</v>
-      </c>
-      <c r="C46" s="18">
-        <v>800</v>
-      </c>
-      <c r="D46" s="18">
-        <v>350</v>
-      </c>
-      <c r="E46" s="19" t="s">
-        <v>116</v>
-      </c>
-      <c r="F46" s="19" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="20">
-        <v>45</v>
-      </c>
-      <c r="B47" s="17">
-        <v>250</v>
-      </c>
-      <c r="C47" s="18">
-        <v>600</v>
-      </c>
-      <c r="D47" s="18">
-        <v>200</v>
-      </c>
-      <c r="E47" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="F47" s="19" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="20">
-        <v>46</v>
-      </c>
-      <c r="B48" s="17">
-        <v>400</v>
-      </c>
-      <c r="C48" s="18">
-        <v>400</v>
-      </c>
-      <c r="D48" s="18">
-        <v>200</v>
-      </c>
-      <c r="E48" s="19" t="s">
-        <v>120</v>
-      </c>
-      <c r="F48" s="19" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="20">
-        <v>47</v>
-      </c>
-      <c r="B49" s="17">
-        <v>250</v>
-      </c>
-      <c r="C49" s="18">
-        <v>400</v>
-      </c>
-      <c r="D49" s="18">
-        <v>50</v>
-      </c>
-      <c r="E49" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="F49" s="19" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="20">
-        <v>48</v>
-      </c>
-      <c r="B50" s="17">
-        <v>400</v>
-      </c>
-      <c r="C50" s="18">
-        <v>600</v>
-      </c>
-      <c r="D50" s="18">
-        <v>350</v>
-      </c>
-      <c r="E50" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="F50" s="19" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="20">
-        <v>49</v>
-      </c>
-      <c r="B51" s="17">
-        <v>250</v>
-      </c>
-      <c r="C51" s="18">
-        <v>400</v>
-      </c>
-      <c r="D51" s="18">
-        <v>350</v>
-      </c>
-      <c r="E51" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="F51" s="19" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="20">
-        <v>50</v>
-      </c>
-      <c r="B52" s="17">
-        <v>100</v>
-      </c>
-      <c r="C52" s="18">
-        <v>400</v>
-      </c>
-      <c r="D52" s="18">
-        <v>200</v>
-      </c>
-      <c r="E52" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="F52" s="19" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="20">
-        <v>51</v>
-      </c>
-      <c r="B53" s="17">
-        <v>100</v>
-      </c>
-      <c r="C53" s="18">
-        <v>800</v>
-      </c>
-      <c r="D53" s="18">
-        <v>200</v>
-      </c>
-      <c r="E53" s="19" t="s">
-        <v>130</v>
-      </c>
-      <c r="F53" s="19" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="20">
-        <v>52</v>
-      </c>
-      <c r="B54" s="17">
-        <v>400</v>
-      </c>
-      <c r="C54" s="18">
-        <v>600</v>
-      </c>
-      <c r="D54" s="18">
-        <v>50</v>
-      </c>
-      <c r="E54" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="F54" s="19" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="20">
-        <v>53</v>
-      </c>
-      <c r="B55" s="17">
-        <v>400</v>
-      </c>
-      <c r="C55" s="18">
-        <v>800</v>
-      </c>
-      <c r="D55" s="18">
-        <v>200</v>
-      </c>
-      <c r="E55" s="19" t="s">
-        <v>134</v>
-      </c>
-      <c r="F55" s="19" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="20">
-        <v>54</v>
-      </c>
-      <c r="B56" s="17">
-        <v>100</v>
-      </c>
-      <c r="C56" s="18">
-        <v>600</v>
-      </c>
-      <c r="D56" s="18">
-        <v>350</v>
-      </c>
-      <c r="E56" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="F56" s="19" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="20">
-        <v>55</v>
-      </c>
-      <c r="B57" s="17">
-        <v>100</v>
-      </c>
-      <c r="C57" s="18">
-        <v>600</v>
-      </c>
-      <c r="D57" s="18">
-        <v>50</v>
-      </c>
-      <c r="E57" s="19" t="s">
-        <v>138</v>
-      </c>
-      <c r="F57" s="19" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="20">
-        <v>56</v>
-      </c>
-      <c r="B58" s="17">
-        <v>250</v>
-      </c>
-      <c r="C58" s="18">
-        <v>600</v>
-      </c>
-      <c r="D58" s="18">
-        <v>200</v>
-      </c>
-      <c r="E58" s="19" t="s">
-        <v>140</v>
-      </c>
-      <c r="F58" s="19" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="20">
-        <v>57</v>
-      </c>
-      <c r="B59" s="17">
-        <v>250</v>
-      </c>
-      <c r="C59" s="18">
-        <v>800</v>
-      </c>
-      <c r="D59" s="18">
-        <v>50</v>
-      </c>
-      <c r="E59" s="19" t="s">
-        <v>142</v>
-      </c>
-      <c r="F59" s="19" t="s">
-        <v>143</v>
-      </c>
+    <row r="45" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="20"/>
+      <c r="B45" s="14"/>
+      <c r="C45" s="15"/>
+      <c r="D45" s="15"/>
+      <c r="E45" s="16"/>
+      <c r="F45" s="16"/>
+    </row>
+    <row r="46" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="20"/>
+      <c r="B46" s="17"/>
+      <c r="C46" s="18"/>
+      <c r="D46" s="18"/>
+      <c r="E46" s="19"/>
+      <c r="F46" s="19"/>
+    </row>
+    <row r="47" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="20"/>
+      <c r="B47" s="17"/>
+      <c r="C47" s="18"/>
+      <c r="D47" s="18"/>
+      <c r="E47" s="19"/>
+      <c r="F47" s="19"/>
+    </row>
+    <row r="48" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="20"/>
+      <c r="B48" s="17"/>
+      <c r="C48" s="18"/>
+      <c r="D48" s="18"/>
+      <c r="E48" s="19"/>
+      <c r="F48" s="19"/>
+    </row>
+    <row r="49" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="20"/>
+      <c r="B49" s="17"/>
+      <c r="C49" s="18"/>
+      <c r="D49" s="18"/>
+      <c r="E49" s="19"/>
+      <c r="F49" s="19"/>
+    </row>
+    <row r="50" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="20"/>
+      <c r="B50" s="17"/>
+      <c r="C50" s="18"/>
+      <c r="D50" s="18"/>
+      <c r="E50" s="19"/>
+      <c r="F50" s="19"/>
+    </row>
+    <row r="51" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="20"/>
+      <c r="B51" s="17"/>
+      <c r="C51" s="18"/>
+      <c r="D51" s="18"/>
+      <c r="E51" s="19"/>
+      <c r="F51" s="19"/>
+    </row>
+    <row r="52" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="20"/>
+      <c r="B52" s="17"/>
+      <c r="C52" s="18"/>
+      <c r="D52" s="18"/>
+      <c r="E52" s="19"/>
+      <c r="F52" s="19"/>
+    </row>
+    <row r="53" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="20"/>
+      <c r="B53" s="17"/>
+      <c r="C53" s="18"/>
+      <c r="D53" s="18"/>
+      <c r="E53" s="19"/>
+      <c r="F53" s="19"/>
+    </row>
+    <row r="54" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="20"/>
+      <c r="B54" s="17"/>
+      <c r="C54" s="18"/>
+      <c r="D54" s="18"/>
+      <c r="E54" s="19"/>
+      <c r="F54" s="19"/>
+    </row>
+    <row r="55" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="20"/>
+      <c r="B55" s="17"/>
+      <c r="C55" s="18"/>
+      <c r="D55" s="18"/>
+      <c r="E55" s="19"/>
+      <c r="F55" s="19"/>
+    </row>
+    <row r="56" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="20"/>
+      <c r="B56" s="17"/>
+      <c r="C56" s="18"/>
+      <c r="D56" s="18"/>
+      <c r="E56" s="19"/>
+      <c r="F56" s="19"/>
+    </row>
+    <row r="57" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="20"/>
+      <c r="B57" s="17"/>
+      <c r="C57" s="18"/>
+      <c r="D57" s="18"/>
+      <c r="E57" s="19"/>
+      <c r="F57" s="19"/>
+    </row>
+    <row r="58" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="20"/>
+      <c r="B58" s="17"/>
+      <c r="C58" s="18"/>
+      <c r="D58" s="18"/>
+      <c r="E58" s="19"/>
+      <c r="F58" s="19"/>
+    </row>
+    <row r="59" spans="1:6" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="20"/>
+      <c r="B59" s="17"/>
+      <c r="C59" s="18"/>
+      <c r="D59" s="18"/>
+      <c r="E59" s="19"/>
+      <c r="F59" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="7">
